--- a/Result/profitability/6176.xlsx
+++ b/Result/profitability/6176.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.84</v>
       </c>
       <c r="M2" t="n">
-        <v>2.5125</v>
+        <v>2.1225</v>
       </c>
       <c r="N2" t="n">
-        <v>19.97125</v>
+        <v>19.8775</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.06</v>
       </c>
       <c r="M3" t="n">
-        <v>2.19</v>
+        <v>1.76375</v>
       </c>
       <c r="N3" t="n">
-        <v>18.51875</v>
+        <v>18.65625</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.13</v>
       </c>
       <c r="M4" t="n">
-        <v>1.84</v>
+        <v>1.63</v>
       </c>
       <c r="N4" t="n">
-        <v>17.48625</v>
+        <v>17.68</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.13</v>
       </c>
       <c r="M5" t="n">
-        <v>1.58125</v>
+        <v>1.43375</v>
       </c>
       <c r="N5" t="n">
-        <v>15.94</v>
+        <v>15.9325</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.24</v>
       </c>
       <c r="M6" t="n">
-        <v>1.37125</v>
+        <v>1.02375</v>
       </c>
       <c r="N6" t="n">
-        <v>13.89625</v>
+        <v>13.68125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.57</v>
       </c>
       <c r="M7" t="n">
-        <v>1.03</v>
+        <v>0.8474999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>12.0925</v>
+        <v>12.125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.24</v>
       </c>
       <c r="M8" t="n">
-        <v>0.9374999999999999</v>
+        <v>0.7162500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>10.85875</v>
+        <v>10.73375</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>1.26</v>
       </c>
       <c r="M9" t="n">
-        <v>0.8087499999999999</v>
+        <v>0.80875</v>
       </c>
       <c r="N9" t="n">
         <v>9.376249999999999</v>
@@ -9344,27 +9344,27 @@
         <v>21.45</v>
       </c>
       <c r="G71" t="n">
-        <v>1726</v>
+        <v>1627</v>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>13.73%</t>
+          <t>12.95%</t>
         </is>
       </c>
       <c r="I71" t="n">
         <v>-299</v>
       </c>
       <c r="J71" t="n">
-        <v>1427</v>
+        <v>1328</v>
       </c>
       <c r="K71" t="n">
-        <v>887</v>
+        <v>787</v>
       </c>
       <c r="L71" t="n">
-        <v>1.92</v>
+        <v>1.7</v>
       </c>
       <c r="M71" t="n">
-        <v>3.08875</v>
+        <v>3.06125</v>
       </c>
       <c r="N71" t="n">
         <v>20.6975</v>
@@ -9394,10 +9394,10 @@
         <v>114.2</v>
       </c>
       <c r="W71" t="n">
-        <v>-0.2800000000000002</v>
+        <v>-0.5000000000000002</v>
       </c>
       <c r="X71" t="n">
-        <v>-0.1272727272727274</v>
+        <v>-0.2272727272727274</v>
       </c>
       <c r="Y71" t="n">
         <v>1.609999999999999</v>
@@ -9406,10 +9406,10 @@
         <v>0.08114919354838701</v>
       </c>
       <c r="AA71" t="n">
-        <v>-1.95</v>
+        <v>-2.17</v>
       </c>
       <c r="AB71" t="n">
-        <v>-0.5038759689922481</v>
+        <v>-0.5607235142118863</v>
       </c>
       <c r="AC71" t="n">
         <v>0.7799999999999976</v>
@@ -9471,24 +9471,24 @@
         <v>23.11</v>
       </c>
       <c r="G72" t="n">
-        <v>1856</v>
+        <v>1954</v>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>14.78%</t>
+          <t>15.56%</t>
         </is>
       </c>
       <c r="I72" t="n">
         <v>296</v>
       </c>
       <c r="J72" t="n">
-        <v>2152</v>
+        <v>2250</v>
       </c>
       <c r="K72" t="n">
-        <v>1518</v>
+        <v>1618</v>
       </c>
       <c r="L72" t="n">
-        <v>3.3</v>
+        <v>3.52</v>
       </c>
       <c r="M72" t="n">
         <v>2.98875</v>
@@ -9521,10 +9521,10 @@
         <v>114.3</v>
       </c>
       <c r="W72" t="n">
-        <v>1.38</v>
+        <v>1.82</v>
       </c>
       <c r="X72" t="n">
-        <v>0.71875</v>
+        <v>1.070588235294118</v>
       </c>
       <c r="Y72" t="n">
         <v>1.66</v>
@@ -9533,10 +9533,10 @@
         <v>0.07738927738927748</v>
       </c>
       <c r="AA72" t="n">
-        <v>-0.3400000000000003</v>
+        <v>-0.1200000000000001</v>
       </c>
       <c r="AB72" t="n">
-        <v>-0.09340659340659352</v>
+        <v>-0.03296703296703296</v>
       </c>
       <c r="AC72" t="n">
         <v>0.9699999999999989</v>
@@ -9648,10 +9648,10 @@
         <v>114.4</v>
       </c>
       <c r="W73" t="n">
-        <v>-1.32</v>
+        <v>-1.54</v>
       </c>
       <c r="X73" t="n">
-        <v>-0.4</v>
+        <v>-0.4375</v>
       </c>
       <c r="Y73" t="n">
         <v>-1.98</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>6176</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11078</v>
+      </c>
+      <c r="D75" t="n">
+        <v>8709</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2370</v>
+      </c>
+      <c r="F75" t="n">
+        <v>21.39</v>
+      </c>
+      <c r="G75" t="n">
+        <v>901</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.13%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-222</v>
+      </c>
+      <c r="J75" t="n">
+        <v>679</v>
+      </c>
+      <c r="K75" t="n">
+        <v>240</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="M75" t="n">
+        <v>2.4725</v>
+      </c>
+      <c r="N75" t="n">
+        <v>21.4675</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.7729257641921398</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.04466279589102273</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.6941176470588235</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-0.05999999999999872</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.002797202797202747</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
